--- a/TASK2/Scenariji/SC08_GenerisanjeStatistike.xlsx
+++ b/TASK2/Scenariji/SC08_GenerisanjeStatistike.xlsx
@@ -473,7 +473,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Administrator generira izvjestaje o poslovanju teretane za odabrani vremenski period.</t>
+          <t>Administrator generiše izvjestaje o poslovanju teretane za odabrani vremenski period.</t>
         </is>
       </c>
     </row>
@@ -504,19 +504,19 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Posljedice - uspjesan zavrsetak</t>
+          <t>Posljedice - uspješan završetak</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Izvjestaj je generisan i prikazan tabelarno/graficki.</t>
+          <t>Izvjestaj je generisan i prikazan tabelarno/grafički.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Posljedice - neuspjesan zavrsetak</t>
+          <t>Posljedice - neuspješan završetak</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Administrator bira tip izvjestaja i period, sistem generira i prikazuje rezultate.</t>
+          <t>Administrator bira tip izvjestaja i period, sistem generiše i prikazuje rezultate.</t>
         </is>
       </c>
     </row>
@@ -573,6 +573,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
@@ -595,7 +596,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>1. Pokretanje opcije za generisanje izvjestaja</t>
+          <t>1. Pokretanje opcije za Generisanje izvjestaja</t>
         </is>
       </c>
     </row>
@@ -630,7 +631,7 @@
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>6. Dohvatanje relevantnih podataka iz baze</t>
+          <t>6. Dohvaćanje relevantnih podataka iz baze</t>
         </is>
       </c>
     </row>
@@ -655,6 +656,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
